--- a/data/trans_orig/Q64D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar</t>
+          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar (tasa de respuesta: 88,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,36</t>
+          <t>4,52; 8,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,44</t>
+          <t>6,25; 13,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 12,32</t>
+          <t>6,96; 12,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 21,49</t>
+          <t>13,26; 21,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,25</t>
+          <t>4,72; 10,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,84</t>
+          <t>5,62; 11,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,95</t>
+          <t>4,89; 10,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,49; 25,72</t>
+          <t>14,39; 25,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,06</t>
+          <t>4,88; 8,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,48</t>
+          <t>6,36; 11,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,29</t>
+          <t>6,77; 10,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 21,76</t>
+          <t>14,98; 21,38</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 15,72</t>
+          <t>8,33; 14,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,62</t>
+          <t>6,1; 10,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 17,25</t>
+          <t>9,84; 18,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 22,03</t>
+          <t>5,14; 21,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 12,92</t>
+          <t>7,41; 12,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,22</t>
+          <t>5,27; 9,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 12,25</t>
+          <t>7,5; 12,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 18,44</t>
+          <t>12,88; 18,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,59</t>
+          <t>8,53; 13,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,22</t>
+          <t>6,08; 9,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 14,25</t>
+          <t>9,58; 14,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 19,24</t>
+          <t>6,91; 19,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,01</t>
+          <t>8,02; 12,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 14,45</t>
+          <t>8,1; 14,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,64</t>
+          <t>5,73; 10,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 17,04</t>
+          <t>9,86; 16,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,78</t>
+          <t>6,38; 12,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 12,29</t>
+          <t>6,25; 12,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,5</t>
+          <t>5,44; 9,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,36</t>
+          <t>10,97; 16,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 11,74</t>
+          <t>8,13; 11,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,82</t>
+          <t>8,16; 12,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,22</t>
+          <t>6,18; 9,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,42</t>
+          <t>11,29; 15,41</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 14,59</t>
+          <t>9,24; 14,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,21</t>
+          <t>6,65; 10,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,28</t>
+          <t>7,21; 12,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 25,47</t>
+          <t>18,07; 25,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,69</t>
+          <t>6,42; 10,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,94</t>
+          <t>7,53; 12,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 19,83</t>
+          <t>11,95; 20,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 21,28</t>
+          <t>9,52; 21,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 12,0</t>
+          <t>8,46; 11,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,71</t>
+          <t>7,67; 10,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 14,79</t>
+          <t>10,28; 15,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,62</t>
+          <t>13,58; 21,78</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,53</t>
+          <t>8,67; 11,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,43</t>
+          <t>7,7; 10,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 11,4</t>
+          <t>8,67; 11,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,74; 19,33</t>
+          <t>9,41; 19,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,9</t>
+          <t>7,29; 9,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,98</t>
+          <t>7,23; 9,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,15</t>
+          <t>8,88; 11,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,08; 17,92</t>
+          <t>12,93; 17,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,64</t>
+          <t>8,46; 10,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 9,69</t>
+          <t>7,85; 9,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 11,32</t>
+          <t>9,08; 11,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,73; 17,89</t>
+          <t>11,62; 17,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,02</t>
+          <t>16,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,82</t>
+          <t>19,18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,86</t>
+          <t>17,78</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,8</t>
+          <t>4,56; 8,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 13,48</t>
+          <t>6,01; 13,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 12,28</t>
+          <t>6,99; 12,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,79</t>
+          <t>12,75; 20,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 10,44</t>
+          <t>4,77; 10,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 11,09</t>
+          <t>5,51; 10,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,33</t>
+          <t>5,07; 10,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 25,57</t>
+          <t>14,83; 26,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,26</t>
+          <t>4,93; 8,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,39</t>
+          <t>6,56; 11,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 10,36</t>
+          <t>6,7; 10,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,38</t>
+          <t>14,83; 21,83</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,13</t>
+          <t>19,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>15,53</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>17,82</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 14,99</t>
+          <t>8,26; 14,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 10,28</t>
+          <t>5,99; 10,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,27</t>
+          <t>9,85; 17,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 21,61</t>
+          <t>16,64; 23,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 12,71</t>
+          <t>7,47; 12,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,77</t>
+          <t>5,12; 10,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,22</t>
+          <t>7,52; 12,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,88; 18,38</t>
+          <t>12,99; 18,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,41</t>
+          <t>8,55; 13,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,16</t>
+          <t>6,07; 9,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 14,53</t>
+          <t>9,23; 13,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 19,16</t>
+          <t>15,58; 20,02</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,09</t>
+          <t>13,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,29</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,19</t>
+          <t>13,71</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,95</t>
+          <t>8,03; 12,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,95</t>
+          <t>8,28; 15,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,21</t>
+          <t>5,88; 10,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 16,43</t>
+          <t>10,22; 16,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 12,04</t>
+          <t>6,48; 11,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,25</t>
+          <t>6,42; 12,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,61</t>
+          <t>5,3; 9,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,57</t>
+          <t>11,42; 17,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,91</t>
+          <t>8,06; 11,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 12,79</t>
+          <t>7,97; 12,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,31</t>
+          <t>6,14; 9,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,41</t>
+          <t>11,6; 15,83</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,25</t>
+          <t>22,0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,09</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,55</t>
+          <t>20,36</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,25</t>
+          <t>9,16; 14,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,87</t>
+          <t>6,73; 10,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 12,53</t>
+          <t>7,21; 12,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,07; 25,35</t>
+          <t>18,44; 25,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,88</t>
+          <t>6,23; 10,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,95</t>
+          <t>7,68; 12,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,95; 20,0</t>
+          <t>11,84; 19,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,52; 21,18</t>
+          <t>15,69; 22,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 11,97</t>
+          <t>8,47; 11,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,93</t>
+          <t>7,53; 10,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,17</t>
+          <t>10,25; 14,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 21,78</t>
+          <t>18,08; 22,85</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,69</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,72</t>
+          <t>16,76</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>17,65</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,53</t>
+          <t>8,81; 11,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,39</t>
+          <t>7,66; 10,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,72</t>
+          <t>8,71; 11,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 19,21</t>
+          <t>16,56; 20,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,89</t>
+          <t>7,32; 9,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 9,88</t>
+          <t>7,17; 10,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 11,95</t>
+          <t>8,88; 12,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,98</t>
+          <t>15,24; 18,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 10,52</t>
+          <t>8,59; 10,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 9,75</t>
+          <t>7,86; 9,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 11,26</t>
+          <t>9,01; 11,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,62; 17,87</t>
+          <t>16,39; 18,98</t>
         </is>
       </c>
     </row>
